--- a/output/pdf_financials_xlsx/VAL.P.xlsx
+++ b/output/pdf_financials_xlsx/VAL.P.xlsx
@@ -3108,19 +3108,19 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.155267</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.155267</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.155267</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.155267</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.155267</v>
       </c>
     </row>
     <row r="93">
@@ -4744,7 +4744,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5069,7 +5073,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VAL.P.xlsx
+++ b/output/pdf_financials_xlsx/VAL.P.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.000418</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.027641</v>
+        <v>0.059601</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.036142</v>
+        <v>0.200211</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.016417</v>
+        <v>0.081662</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.016129</v>
+        <v>0.087241</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.015914</v>
+        <v>0.110627</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.019883</v>
+        <v>0.084484</v>
       </c>
     </row>
     <row r="11">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-0.000418</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.027641</v>
+        <v>-0.059601</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.036142</v>
+        <v>-0.200211</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.016417</v>
+        <v>-0.081662</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.016129</v>
+        <v>-0.087241</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.015914</v>
+        <v>-0.110627</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.019883</v>
+        <v>-0.084484</v>
       </c>
     </row>
     <row r="12">
@@ -1394,25 +1394,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.124996</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.048431</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.7265509999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.647358</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.560961</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.453767</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.373594</v>
       </c>
     </row>
     <row r="35">
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.124996</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.048431</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.7265509999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.647358</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.560961</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.453767</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.373594</v>
       </c>
     </row>
     <row r="37">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">

--- a/output/pdf_financials_xlsx/VAL.P.xlsx
+++ b/output/pdf_financials_xlsx/VAL.P.xlsx
@@ -3336,22 +3336,22 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001292</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.001292</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000874</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003351</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.004065</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003409</v>
       </c>
     </row>
     <row r="102">
@@ -3476,22 +3476,22 @@
         <v>0.000414</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.013172</v>
+        <v>-0.014464</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.041187</v>
+        <v>0.042479</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.028157</v>
+        <v>-0.029031</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.004195</v>
+        <v>0.000844</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.000632</v>
+        <v>0.003433</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.00772</v>
+        <v>0.004311</v>
       </c>
     </row>
     <row r="107">
@@ -5277,7 +5277,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
